--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126827426</v>
+        <v>126827104</v>
       </c>
       <c r="B4" t="n">
-        <v>95604</v>
+        <v>96039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334770</v>
+        <v>334685</v>
       </c>
       <c r="R4" t="n">
-        <v>6444214</v>
+        <v>6444141</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126827104</v>
+        <v>126827426</v>
       </c>
       <c r="B5" t="n">
-        <v>95964</v>
+        <v>95679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334685</v>
+        <v>334770</v>
       </c>
       <c r="R5" t="n">
-        <v>6444141</v>
+        <v>6444214</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>126826137</v>
       </c>
       <c r="B6" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>126826329</v>
       </c>
       <c r="B8" t="n">
-        <v>95604</v>
+        <v>95679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>127095233</v>
       </c>
       <c r="B12" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>127094388</v>
       </c>
       <c r="B13" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126827104</v>
       </c>
       <c r="B4" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126827426</v>
       </c>
       <c r="B5" t="n">
-        <v>95679</v>
+        <v>95685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126826137</v>
       </c>
       <c r="B6" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>126826329</v>
       </c>
       <c r="B8" t="n">
-        <v>95679</v>
+        <v>95685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>127095233</v>
       </c>
       <c r="B12" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>127094388</v>
       </c>
       <c r="B13" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127093253</v>
+        <v>127098179</v>
       </c>
       <c r="B10" t="n">
         <v>57654</v>
@@ -1565,24 +1565,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intagan, Intagan, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334896</v>
+        <v>334772</v>
       </c>
       <c r="R10" t="n">
-        <v>6444155</v>
+        <v>6444116</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127098179</v>
+        <v>127093253</v>
       </c>
       <c r="B11" t="n">
         <v>57654</v>
@@ -1677,19 +1677,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334772</v>
+        <v>334896</v>
       </c>
       <c r="R11" t="n">
-        <v>6444116</v>
+        <v>6444155</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,12 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126827104</v>
       </c>
       <c r="B4" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126827426</v>
       </c>
       <c r="B5" t="n">
-        <v>95685</v>
+        <v>95686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126826137</v>
       </c>
       <c r="B6" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>126826329</v>
       </c>
       <c r="B8" t="n">
-        <v>95685</v>
+        <v>95686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098179</v>
+        <v>127093253</v>
       </c>
       <c r="B10" t="n">
         <v>57654</v>
@@ -1565,19 +1565,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334772</v>
+        <v>334896</v>
       </c>
       <c r="R10" t="n">
-        <v>6444116</v>
+        <v>6444155</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127093253</v>
+        <v>127098179</v>
       </c>
       <c r="B11" t="n">
         <v>57654</v>
@@ -1677,24 +1677,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intagan, Intagan, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334896</v>
+        <v>334772</v>
       </c>
       <c r="R11" t="n">
-        <v>6444155</v>
+        <v>6444116</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1728,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1763,7 @@
         <v>127095233</v>
       </c>
       <c r="B12" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>127094388</v>
       </c>
       <c r="B13" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826202</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126827253</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126827104</v>
+        <v>126827426</v>
       </c>
       <c r="B4" t="n">
-        <v>96046</v>
+        <v>95690</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334685</v>
+        <v>334770</v>
       </c>
       <c r="R4" t="n">
-        <v>6444141</v>
+        <v>6444214</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126827426</v>
+        <v>126827104</v>
       </c>
       <c r="B5" t="n">
-        <v>95686</v>
+        <v>96050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334770</v>
+        <v>334685</v>
       </c>
       <c r="R5" t="n">
-        <v>6444214</v>
+        <v>6444141</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>126826137</v>
       </c>
       <c r="B6" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>126827000</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>126826329</v>
       </c>
       <c r="B8" t="n">
-        <v>95686</v>
+        <v>95690</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127097494</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>127093253</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127098179</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>127095233</v>
       </c>
       <c r="B12" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>127094388</v>
       </c>
       <c r="B13" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>127093965</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>127097517</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127097359</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>127095024</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>127096416</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126827426</v>
+        <v>126827104</v>
       </c>
       <c r="B4" t="n">
-        <v>95690</v>
+        <v>96050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334770</v>
+        <v>334685</v>
       </c>
       <c r="R4" t="n">
-        <v>6444214</v>
+        <v>6444141</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126827104</v>
+        <v>126827426</v>
       </c>
       <c r="B5" t="n">
-        <v>96050</v>
+        <v>95690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334685</v>
+        <v>334770</v>
       </c>
       <c r="R5" t="n">
-        <v>6444141</v>
+        <v>6444214</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127093253</v>
+        <v>127098179</v>
       </c>
       <c r="B10" t="n">
         <v>57658</v>
@@ -1565,24 +1565,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intagan, Intagan, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334896</v>
+        <v>334772</v>
       </c>
       <c r="R10" t="n">
-        <v>6444155</v>
+        <v>6444116</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127098179</v>
+        <v>127093253</v>
       </c>
       <c r="B11" t="n">
         <v>57658</v>
@@ -1677,19 +1677,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334772</v>
+        <v>334896</v>
       </c>
       <c r="R11" t="n">
-        <v>6444116</v>
+        <v>6444155</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,12 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098179</v>
+        <v>127093253</v>
       </c>
       <c r="B10" t="n">
         <v>57658</v>
@@ -1565,19 +1565,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334772</v>
+        <v>334896</v>
       </c>
       <c r="R10" t="n">
-        <v>6444116</v>
+        <v>6444155</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127093253</v>
+        <v>127098179</v>
       </c>
       <c r="B11" t="n">
         <v>57658</v>
@@ -1677,24 +1677,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intagan, Intagan, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334896</v>
+        <v>334772</v>
       </c>
       <c r="R11" t="n">
-        <v>6444155</v>
+        <v>6444116</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1728,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -1427,7 +1427,7 @@
         <v>127097494</v>
       </c>
       <c r="B9" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>127093253</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127098179</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>127095233</v>
       </c>
       <c r="B12" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>127094388</v>
       </c>
       <c r="B13" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>127093965</v>
       </c>
       <c r="B14" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>127097517</v>
       </c>
       <c r="B15" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127097359</v>
       </c>
       <c r="B16" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>127095024</v>
       </c>
       <c r="B17" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>127096416</v>
       </c>
       <c r="B18" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126827253</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1424,48 +1424,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127097494</v>
+        <v>127093253</v>
       </c>
       <c r="B9" t="n">
-        <v>56855</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>334772</v>
+        <v>334896</v>
       </c>
       <c r="R9" t="n">
-        <v>6444116</v>
+        <v>6444155</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Medelfärsk spillning av tjäder</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127093253</v>
+        <v>127098179</v>
       </c>
       <c r="B10" t="n">
         <v>57660</v>
@@ -1565,24 +1565,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intagan, Intagan, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334896</v>
+        <v>334772</v>
       </c>
       <c r="R10" t="n">
-        <v>6444155</v>
+        <v>6444116</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,45 +1648,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127098179</v>
+        <v>127095233</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>96058</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Grönedal, Grönedal, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334772</v>
+        <v>334473</v>
       </c>
       <c r="R11" t="n">
-        <v>6444116</v>
+        <v>6444292</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,12 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127095233</v>
+        <v>127094388</v>
       </c>
       <c r="B12" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,14 +1786,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grönedal, Grönedal, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>334473</v>
+        <v>334772</v>
       </c>
       <c r="R12" t="n">
-        <v>6444292</v>
+        <v>6444116</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,22 +1850,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127094388</v>
+        <v>127097494</v>
       </c>
       <c r="B13" t="n">
-        <v>96052</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Medelfärsk spillning av tjäder</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126827253</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127093253</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>127098179</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127095233</v>
       </c>
       <c r="B11" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127094388</v>
       </c>
       <c r="B12" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127097494</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>127093965</v>
       </c>
       <c r="B14" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>127097517</v>
       </c>
       <c r="B15" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127097359</v>
       </c>
       <c r="B16" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>127095024</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>127096416</v>
       </c>
       <c r="B18" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126827253</v>
       </c>
       <c r="B3" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127093253</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>127098179</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127095233</v>
       </c>
       <c r="B11" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127094388</v>
       </c>
       <c r="B12" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127097494</v>
       </c>
       <c r="B13" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>127093965</v>
       </c>
       <c r="B14" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>127097517</v>
       </c>
       <c r="B15" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127097359</v>
       </c>
       <c r="B16" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>127095024</v>
       </c>
       <c r="B17" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>127096416</v>
       </c>
       <c r="B18" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126827253</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127097494</v>
       </c>
       <c r="B13" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>127093965</v>
       </c>
       <c r="B14" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>127097517</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127097359</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>127095024</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>127096416</v>
       </c>
       <c r="B18" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126827253</v>
       </c>
       <c r="B3" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127097494</v>
       </c>
       <c r="B13" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>127093965</v>
       </c>
       <c r="B14" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>127097517</v>
       </c>
       <c r="B15" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127097359</v>
       </c>
       <c r="B16" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>127095024</v>
       </c>
       <c r="B17" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>127096416</v>
       </c>
       <c r="B18" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826202</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126827104</v>
       </c>
       <c r="B4" t="n">
-        <v>96050</v>
+        <v>96039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126827426</v>
       </c>
       <c r="B5" t="n">
-        <v>95690</v>
+        <v>95679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126826137</v>
       </c>
       <c r="B6" t="n">
-        <v>96050</v>
+        <v>96039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>126827000</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>126826329</v>
       </c>
       <c r="B8" t="n">
-        <v>95690</v>
+        <v>95679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,53 +1424,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127093253</v>
+        <v>127097494</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>56880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Intagan, Intagan, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>334896</v>
+        <v>334772</v>
       </c>
       <c r="R9" t="n">
-        <v>6444155</v>
+        <v>6444116</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Medelfärsk spillning av tjäder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098179</v>
+        <v>127093253</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,19 +1565,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334772</v>
+        <v>334896</v>
       </c>
       <c r="R10" t="n">
-        <v>6444116</v>
+        <v>6444155</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,45 +1648,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127095233</v>
+        <v>127098179</v>
       </c>
       <c r="B11" t="n">
-        <v>96069</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grönedal, Grönedal, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334473</v>
+        <v>334772</v>
       </c>
       <c r="R11" t="n">
-        <v>6444292</v>
+        <v>6444116</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1748,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127094388</v>
+        <v>127095233</v>
       </c>
       <c r="B12" t="n">
-        <v>96069</v>
+        <v>96039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,14 +1791,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Grönedal, Grönedal, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>334772</v>
+        <v>334473</v>
       </c>
       <c r="R12" t="n">
-        <v>6444116</v>
+        <v>6444292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,22 +1855,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127097494</v>
+        <v>127094388</v>
       </c>
       <c r="B13" t="n">
-        <v>56880</v>
+        <v>96039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Medelfärsk spillning av tjäder</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126826202</v>
+        <v>126826137</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334853</v>
+        <v>334894</v>
       </c>
       <c r="R2" t="n">
-        <v>6444153</v>
+        <v>6444117</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126827253</v>
+        <v>126827104</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334718</v>
+        <v>334685</v>
       </c>
       <c r="R3" t="n">
-        <v>6444151</v>
+        <v>6444141</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126827104</v>
+        <v>127094388</v>
       </c>
       <c r="B4" t="n">
-        <v>96050</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Intagan, Intagan, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334685</v>
+        <v>334772</v>
       </c>
       <c r="R4" t="n">
-        <v>6444141</v>
+        <v>6444116</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126827426</v>
+        <v>127095233</v>
       </c>
       <c r="B5" t="n">
-        <v>95690</v>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Intagan, Intagan, Vg</t>
+          <t>Grönedal, Grönedal, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334770</v>
+        <v>334473</v>
       </c>
       <c r="R5" t="n">
-        <v>6444214</v>
+        <v>6444292</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126826137</v>
+        <v>126826329</v>
       </c>
       <c r="B6" t="n">
-        <v>96050</v>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334894</v>
+        <v>334811</v>
       </c>
       <c r="R6" t="n">
-        <v>6444117</v>
+        <v>6444163</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126827000</v>
+        <v>126827426</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>334710</v>
+        <v>334770</v>
       </c>
       <c r="R7" t="n">
-        <v>6444105</v>
+        <v>6444214</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126826329</v>
+        <v>126826202</v>
       </c>
       <c r="B8" t="n">
-        <v>95690</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>334811</v>
+        <v>334853</v>
       </c>
       <c r="R8" t="n">
-        <v>6444163</v>
+        <v>6444153</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127093253</v>
+        <v>126827000</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1453,24 +1453,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>334896</v>
+        <v>334710</v>
       </c>
       <c r="R9" t="n">
-        <v>6444155</v>
+        <v>6444105</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,22 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,26 +1519,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098179</v>
+        <v>127093253</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1565,19 +1560,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334772</v>
+        <v>334896</v>
       </c>
       <c r="R10" t="n">
-        <v>6444116</v>
+        <v>6444155</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka på död gran i kanten av mosse</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127095233</v>
+        <v>127096372</v>
       </c>
       <c r="B11" t="n">
-        <v>96069</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,34 +1654,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grönedal, Grönedal, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334473</v>
+        <v>334772</v>
       </c>
       <c r="R11" t="n">
-        <v>6444292</v>
+        <v>6444116</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1723,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Medelfärskt spår av Födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127094388</v>
+        <v>126827078</v>
       </c>
       <c r="B12" t="n">
-        <v>96069</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,34 +1766,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>334772</v>
+        <v>334677</v>
       </c>
       <c r="R12" t="n">
-        <v>6444116</v>
+        <v>6444083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,22 +1820,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,22 +1850,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127097494</v>
+        <v>126827253</v>
       </c>
       <c r="B13" t="n">
-        <v>56880</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,14 +1893,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Intagan, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>334772</v>
+        <v>334718</v>
       </c>
       <c r="R13" t="n">
-        <v>6444116</v>
+        <v>6444151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,27 +1927,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Medelfärsk spillning av tjäder</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,22 +1957,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127093965</v>
+        <v>127093644</v>
       </c>
       <c r="B14" t="n">
-        <v>56880</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,17 +2000,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grönedal, Grönedal, Vg</t>
+          <t>Intagan, Intagan, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>334618</v>
+        <v>334726</v>
       </c>
       <c r="R14" t="n">
-        <v>6444173</v>
+        <v>6444060</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2074,22 +2069,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127097517</v>
+        <v>127093965</v>
       </c>
       <c r="B15" t="n">
-        <v>56880</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,13 +2116,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>334606</v>
+        <v>334618</v>
       </c>
       <c r="R15" t="n">
-        <v>6444185</v>
+        <v>6444173</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2186,22 +2181,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127097359</v>
+        <v>127095024</v>
       </c>
       <c r="B16" t="n">
-        <v>56880</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,13 +2228,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>334632</v>
+        <v>334508</v>
       </c>
       <c r="R16" t="n">
-        <v>6444209</v>
+        <v>6444278</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2268,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2310,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127095024</v>
+        <v>127095242</v>
       </c>
       <c r="B17" t="n">
-        <v>56880</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,17 +2336,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grönedal, Grönedal, Vg</t>
+          <t>Intagan, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>334508</v>
+        <v>334772</v>
       </c>
       <c r="R17" t="n">
-        <v>6444278</v>
+        <v>6444116</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2380,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2385,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Hyfsat färsk spillning på häll ovan kraftledningen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,12 +2405,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2425,7 +2420,7 @@
         <v>127096416</v>
       </c>
       <c r="B18" t="n">
-        <v>56880</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,6 +2526,230 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127097359</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Grönedal, Grönedal, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>334632</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6444209</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tunge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127097517</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Grönedal, Grönedal, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>334606</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6444185</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tunge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28512-2025 artfynd.xlsx
+++ b/artfynd/A 28512-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126827104</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127094388</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127095233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826329</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126827426</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826202</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126827000</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127093253</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127096372</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126827078</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126827253</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127093644</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127093965</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2302,6 +2377,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127095024</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2414,6 +2494,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127095242</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2526,6 +2611,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127096416</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2638,6 +2728,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127097359</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2750,8 +2845,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127097517</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>